--- a/debug/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Qwen3-Next-80B-A3B-Instruct/metrics_default_vs_aae.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Qwen3-Next-80B-A3B-Instruct/metrics_default_vs_aae.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.6804123711340206</v>
+        <v>0.898989898989899</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.5633802816901409</v>
+        <v>0.7375886524822695</v>
       </c>
       <c r="D2">
-        <v>0.484375</v>
+        <v>0.2936507936507937</v>
       </c>
       <c r="E2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F2">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="G2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/debug/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Qwen3-Next-80B-A3B-Instruct/metrics_default_vs_aae.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Qwen3-Next-80B-A3B-Instruct/metrics_default_vs_aae.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.898989898989899</v>
+        <v>0.9052631578947369</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.7375886524822695</v>
+        <v>0.762589928057554</v>
       </c>
       <c r="D2">
-        <v>0.2936507936507937</v>
+        <v>0.2773109243697479</v>
       </c>
       <c r="E2">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="F2">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G2">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
